--- a/employee_settings.xlsx
+++ b/employee_settings.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T02363\Downloads\ShiftScheduler\"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="52">
   <si>
     <t>emp_id</t>
   </si>
@@ -63,18 +63,12 @@
     <t>NOON</t>
   </si>
   <si>
-    <t>LONG</t>
-  </si>
-  <si>
     <t>T01029</t>
   </si>
   <si>
     <t>林雯琳</t>
   </si>
   <si>
-    <t>SHORT</t>
-  </si>
-  <si>
     <t>T01734</t>
   </si>
   <si>
@@ -175,10 +169,6 @@
   </si>
   <si>
     <t>張雅荃</t>
-  </si>
-  <si>
-    <t>MIX</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>𡍼文妤</t>
@@ -192,7 +182,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1138,10 +1128,10 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1155,13 +1145,13 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1169,10 +1159,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -1180,8 +1170,8 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
-        <v>17</v>
+      <c r="E4">
+        <v>3</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1189,16 +1179,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1209,16 +1199,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1229,16 +1219,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -1249,19 +1239,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1269,10 +1259,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -1289,10 +1279,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -1309,13 +1299,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
         <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
@@ -1329,16 +1319,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -1349,16 +1339,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -1369,19 +1359,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1389,13 +1379,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -1409,16 +1399,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -1429,16 +1419,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -1449,13 +1439,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
@@ -1469,16 +1459,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -1489,13 +1479,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
         <v>13</v>

--- a/employee_settings.xlsx
+++ b/employee_settings.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="76">
   <si>
     <t>emp_id</t>
   </si>
@@ -61,24 +61,6 @@
     <t>ANY</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>ny</t>
-    </r>
-  </si>
-  <si>
     <t>T01029</t>
   </si>
   <si>
@@ -91,48 +73,12 @@
     <t>黃冠銘</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>ny</t>
-    </r>
-  </si>
-  <si>
     <t>T02287</t>
   </si>
   <si>
     <t>林江玉</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>ny</t>
-    </r>
-  </si>
-  <si>
     <t>T02359</t>
   </si>
   <si>
@@ -148,72 +94,18 @@
     <t>NIGHT_ONLY</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>ny</t>
-    </r>
-  </si>
-  <si>
     <t>T02504</t>
   </si>
   <si>
     <t>潘元浩</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>ny</t>
-    </r>
-  </si>
-  <si>
     <t>T02505</t>
   </si>
   <si>
     <t>李慧盺</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>ny</t>
-    </r>
-  </si>
-  <si>
     <t>T02776</t>
   </si>
   <si>
@@ -223,46 +115,10 @@
     <t>MIX</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>ny</t>
-    </r>
-  </si>
-  <si>
     <t>T02777</t>
   </si>
   <si>
     <t>彭裕涵</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>ny</t>
-    </r>
   </si>
   <si>
     <t>T00557</t>
@@ -584,7 +440,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -595,11 +451,6 @@
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -623,7 +474,7 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
@@ -890,7 +741,7 @@
         <v>1.0</v>
       </c>
       <c r="G2" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1">
@@ -912,16 +763,16 @@
       <c r="F3" s="1">
         <v>1.0</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
+      <c r="G3" s="2">
+        <v>1.0</v>
       </c>
     </row>
     <row r="4" ht="16.5" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
@@ -936,15 +787,15 @@
         <v>1.0</v>
       </c>
       <c r="G4" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
@@ -958,16 +809,16 @@
       <c r="F5" s="1">
         <v>1.0</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>21</v>
+      <c r="G5" s="2">
+        <v>1.0</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
@@ -981,16 +832,16 @@
       <c r="F6" s="1">
         <v>1.0</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>24</v>
+      <c r="G6" s="2">
+        <v>1.0</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
@@ -1005,21 +856,21 @@
         <v>1.0</v>
       </c>
       <c r="G7" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1">
         <v>6.0</v>
@@ -1027,16 +878,16 @@
       <c r="F8" s="1">
         <v>1.0</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>30</v>
+      <c r="G8" s="2">
+        <v>1.0</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
@@ -1050,16 +901,16 @@
       <c r="F9" s="1">
         <v>1.0</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>33</v>
+      <c r="G9" s="2">
+        <v>1.0</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>9</v>
@@ -1073,22 +924,22 @@
       <c r="F10" s="1">
         <v>1.0</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>36</v>
+      <c r="G10" s="2">
+        <v>1.0</v>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>15</v>
@@ -1096,22 +947,22 @@
       <c r="F11" s="1">
         <v>1.0</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>40</v>
+      <c r="G11" s="2">
+        <v>1.0</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>15</v>
@@ -1119,22 +970,22 @@
       <c r="F12" s="1">
         <v>1.0</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>43</v>
+      <c r="G12" s="2">
+        <v>1.0</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>15</v>
@@ -1143,18 +994,18 @@
         <v>1.0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
@@ -1166,18 +1017,18 @@
         <v>1.0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
@@ -1189,18 +1040,18 @@
         <v>1.0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
@@ -1212,18 +1063,18 @@
         <v>1.0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>14</v>
@@ -1235,18 +1086,18 @@
         <v>1.0</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
@@ -1258,18 +1109,18 @@
         <v>1.0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -1281,18 +1132,18 @@
         <v>1.0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>14</v>
@@ -1304,18 +1155,18 @@
         <v>1.0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>14</v>
@@ -1327,21 +1178,21 @@
         <v>1.0</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>15</v>
@@ -1350,21 +1201,21 @@
         <v>1.0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>15</v>
@@ -1373,21 +1224,21 @@
         <v>1.0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>15</v>
@@ -1396,21 +1247,21 @@
         <v>1.0</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>15</v>
@@ -1419,7 +1270,7 @@
         <v>1.0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1"/>
